--- a/luutru-prototypes/danh-sach-chuc-nang-storage.xlsx
+++ b/luutru-prototypes/danh-sach-chuc-nang-storage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Study\Personal\Viettel\intern\cloud-drive\luutru-prototypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C50A50F-288E-4297-AF4A-54452E0ED395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECB038D-D3D4-45BA-9297-F5FFD23A3B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Người dùng" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="185">
   <si>
     <t>CHỨC NĂNG CẦN TRIỂN KHAI — NGƯỜI DÙNG</t>
   </si>
@@ -587,6 +587,9 @@
   </si>
   <si>
     <t>Đang thực hiện</t>
+  </si>
+  <si>
+    <t>Hoàn thành</t>
   </si>
 </sst>
 </file>
@@ -1161,7 +1164,9 @@
       <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="9"/>
+      <c r="E9" s="9" t="s">
+        <v>182</v>
+      </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" ht="55" customHeight="1">
@@ -1177,7 +1182,9 @@
       <c r="D10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="9"/>
+      <c r="E10" s="9" t="s">
+        <v>182</v>
+      </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:6" ht="55" customHeight="1">
@@ -2153,7 +2160,9 @@
         <f t="shared" ref="F13:F28" si="0">$B$4</f>
         <v>20</v>
       </c>
-      <c r="G13" s="21"/>
+      <c r="G13" s="21" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="14" spans="1:7" ht="76" customHeight="1">
       <c r="A14" s="17">
@@ -2175,7 +2184,9 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="G14" s="21"/>
+      <c r="G14" s="21" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="15" spans="1:7" ht="76" customHeight="1">
       <c r="A15" s="17">

--- a/luutru-prototypes/danh-sach-chuc-nang-storage.xlsx
+++ b/luutru-prototypes/danh-sach-chuc-nang-storage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Study\Personal\Viettel\intern\cloud-drive\luutru-prototypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DECB038D-D3D4-45BA-9297-F5FFD23A3B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD4D11D-A597-47AB-8964-F10230738C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Người dùng" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="185">
   <si>
     <t>CHỨC NĂNG CẦN TRIỂN KHAI — NGƯỜI DÙNG</t>
   </si>
@@ -1165,7 +1165,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F9" s="9"/>
     </row>
@@ -1183,7 +1183,7 @@
         <v>18</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F10" s="9"/>
     </row>
@@ -1200,7 +1200,9 @@
       <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="9"/>
+      <c r="E11" s="9" t="s">
+        <v>184</v>
+      </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:6" ht="55" customHeight="1">
@@ -1216,7 +1218,9 @@
       <c r="D12" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="9"/>
+      <c r="E12" s="9" t="s">
+        <v>183</v>
+      </c>
       <c r="F12" s="9"/>
     </row>
     <row r="13" spans="1:6" ht="55" customHeight="1">
@@ -1232,7 +1236,9 @@
       <c r="D13" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="9"/>
+      <c r="E13" s="9" t="s">
+        <v>183</v>
+      </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:6" ht="55" customHeight="1">
@@ -1778,7 +1784,9 @@
       <c r="D7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="9"/>
+      <c r="E7" s="9" t="s">
+        <v>184</v>
+      </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:6" ht="55" customHeight="1">
@@ -1794,7 +1802,9 @@
       <c r="D8" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="9" t="s">
+        <v>182</v>
+      </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:6" ht="55" customHeight="1">
@@ -1810,7 +1820,9 @@
       <c r="D9" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="E9" s="9"/>
+      <c r="E9" s="9" t="s">
+        <v>183</v>
+      </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:6" ht="55" customHeight="1">
@@ -2208,7 +2220,9 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="G15" s="21"/>
+      <c r="G15" s="21" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="16" spans="1:7" ht="76" customHeight="1">
       <c r="A16" s="17">

--- a/luutru-prototypes/danh-sach-chuc-nang-storage.xlsx
+++ b/luutru-prototypes/danh-sach-chuc-nang-storage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\Study\Personal\Viettel\intern\cloud-drive\luutru-prototypes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAD4D11D-A597-47AB-8964-F10230738C6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B8DFD0-A95D-4DFF-A2AB-F7CD8476AB51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="186">
   <si>
     <t>CHỨC NĂNG CẦN TRIỂN KHAI — NGƯỜI DÙNG</t>
   </si>
@@ -590,6 +590,9 @@
   </si>
   <si>
     <t>Hoàn thành</t>
+  </si>
+  <si>
+    <t>Chưa bắt đầu</t>
   </si>
 </sst>
 </file>
@@ -1219,7 +1222,7 @@
         <v>22</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F12" s="9"/>
     </row>
@@ -1237,7 +1240,7 @@
         <v>24</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F13" s="9"/>
     </row>
